--- a/dissemination/Brain Tumor Classification Model Comparisons Metrics.xlsx
+++ b/dissemination/Brain Tumor Classification Model Comparisons Metrics.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cochr\Data Science Projects\Brain-Tumor-Detection\dissemination\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{363420C5-2E30-4089-AD16-74F2FD094105}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{087408AD-58C6-4007-9412-93FF4B5BC4F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21240" xr2:uid="{886F016B-F3B6-4904-9251-B24D56E16486}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="9">
   <si>
     <t>Epoch Size</t>
   </si>
@@ -54,6 +54,15 @@
   </si>
   <si>
     <t>1x10-6</t>
+  </si>
+  <si>
+    <t>Var</t>
+  </si>
+  <si>
+    <t>RLROP</t>
+  </si>
+  <si>
+    <t>RLROP + ES</t>
   </si>
 </sst>
 </file>
@@ -141,13 +150,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -165,6 +173,92 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>19050</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>28574</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>190499</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="2" name="TextBox 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{07383DF9-2E04-4781-0758-B661372606B2}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1847850" y="4410074"/>
+          <a:ext cx="2809875" cy="1876425"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+        <a:ln w="9525" cmpd="sng">
+          <a:solidFill>
+            <a:schemeClr val="lt1">
+              <a:shade val="50000"/>
+            </a:schemeClr>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1100" u="sng"/>
+            <a:t>ES</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1100" u="sng" baseline="0"/>
+            <a:t> + RLROP Notes:</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr marL="171450" indent="-171450">
+            <a:buFont typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+            <a:buChar char="•"/>
+          </a:pPr>
+          <a:endParaRPr lang="en-GB" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -484,7 +578,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{157E6442-83B2-458A-A7D7-44481521E105}">
-  <dimension ref="D4:K12"/>
+  <dimension ref="D4:K21"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="4" max="4" width="11.5703125" customWidth="1"/>
@@ -624,12 +718,41 @@
       <c r="K11" s="3"/>
     </row>
     <row r="12" spans="4:11" x14ac:dyDescent="0.25">
-      <c r="J12" s="5">
+      <c r="J12" s="4">
         <v>200</v>
       </c>
       <c r="K12" s="4"/>
+    </row>
+    <row r="17" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D17" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="E17" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="19" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D19" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="E19" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D20" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E20" s="2"/>
+    </row>
+    <row r="21" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D21" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="E21" s="4"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
--- a/dissemination/Brain Tumor Classification Model Comparisons Metrics.xlsx
+++ b/dissemination/Brain Tumor Classification Model Comparisons Metrics.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cochr\Data Science Projects\Brain-Tumor-Detection\dissemination\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{087408AD-58C6-4007-9412-93FF4B5BC4F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F4E7D46-4B15-43C6-81DA-96F97FD80801}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21240" xr2:uid="{886F016B-F3B6-4904-9251-B24D56E16486}"/>
+    <workbookView xWindow="7080" yWindow="1935" windowWidth="38700" windowHeight="15435" xr2:uid="{886F016B-F3B6-4904-9251-B24D56E16486}"/>
   </bookViews>
   <sheets>
     <sheet name="Comparisons" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="10">
   <si>
     <t>Epoch Size</t>
   </si>
@@ -63,6 +63,9 @@
   </si>
   <si>
     <t>RLROP + ES</t>
+  </si>
+  <si>
+    <t>Metrics</t>
   </si>
 </sst>
 </file>
@@ -175,6 +178,6225 @@
 </styleSheet>
 </file>
 
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="1" i="1" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:srgbClr val="FF0000"/>
+                </a:solidFill>
+                <a:latin typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US" b="1" i="1">
+                <a:solidFill>
+                  <a:srgbClr val="FF0000"/>
+                </a:solidFill>
+              </a:rPr>
+              <a:t>LR = 1x10</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="en-US" b="1" i="1" baseline="30000">
+                <a:solidFill>
+                  <a:srgbClr val="FF0000"/>
+                </a:solidFill>
+              </a:rPr>
+              <a:t>-4</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="1" i="1" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+              <a:latin typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout>
+        <c:manualLayout>
+          <c:layoutTarget val="inner"/>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="0.10491983682762546"/>
+          <c:y val="0.12263267998961098"/>
+          <c:w val="0.87299180975871993"/>
+          <c:h val="0.73306160682593824"/>
+        </c:manualLayout>
+      </c:layout>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Comparisons!$E$6</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>F1-Score</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="FF0000"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="1" i="1" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:srgbClr val="FF0000"/>
+                    </a:solidFill>
+                    <a:latin typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="en-US"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="outEnd"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:round/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:numRef>
+              <c:f>Comparisons!$D$7:$D$11</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>30</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>45</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>60</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>100</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Comparisons!$E$7:$E$11</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>0.55000000000000004</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.89</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.89</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.88</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.91</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-3CD2-4EE6-9EC4-8EC0E83C2E73}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:dLblPos val="outEnd"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="1"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="219"/>
+        <c:overlap val="-27"/>
+        <c:axId val="1892425040"/>
+        <c:axId val="1892420240"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="1892425040"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-GB" b="1"/>
+                  <a:t>Epoch Size</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1892420240"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="1892420240"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-GB" b="1"/>
+                  <a:t>F1-Score</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:layout>
+            <c:manualLayout>
+              <c:xMode val="edge"/>
+              <c:yMode val="edge"/>
+              <c:x val="2.1876740216860445E-2"/>
+              <c:y val="0.39214425435655359"/>
+            </c:manualLayout>
+          </c:layout>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1892425040"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr>
+          <a:latin typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+          <a:cs typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+        </a:defRPr>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="1" i="1" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:srgbClr val="00B050"/>
+                </a:solidFill>
+                <a:latin typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US" b="1" i="1">
+                <a:solidFill>
+                  <a:srgbClr val="00B050"/>
+                </a:solidFill>
+              </a:rPr>
+              <a:t>LR = 1x10</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="en-US" b="1" i="1" baseline="30000">
+                <a:solidFill>
+                  <a:srgbClr val="00B050"/>
+                </a:solidFill>
+              </a:rPr>
+              <a:t>-5</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="1" i="1" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:srgbClr val="00B050"/>
+              </a:solidFill>
+              <a:latin typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout>
+        <c:manualLayout>
+          <c:layoutTarget val="inner"/>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="0.10491983682762546"/>
+          <c:y val="0.12263267998961098"/>
+          <c:w val="0.87299180975871993"/>
+          <c:h val="0.73306160682593824"/>
+        </c:manualLayout>
+      </c:layout>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Comparisons!$H$6</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>F1-Score</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="00B050"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="1" i="1" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:srgbClr val="00B050"/>
+                    </a:solidFill>
+                    <a:latin typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="en-US"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="outEnd"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:round/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:numRef>
+              <c:f>Comparisons!$G$7:$G$11</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>30</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>45</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>60</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>100</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Comparisons!$H$7:$H$11</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>0.68</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.82</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.82</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.86</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.85</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-73D6-4F84-8A80-9F3C5FC8C0FC}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:dLblPos val="outEnd"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="1"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="219"/>
+        <c:overlap val="-27"/>
+        <c:axId val="1892425040"/>
+        <c:axId val="1892420240"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="1892425040"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-GB" b="1"/>
+                  <a:t>Epoch Size</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1892420240"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="1892420240"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-GB" b="1"/>
+                  <a:t>F1-Score</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:layout>
+            <c:manualLayout>
+              <c:xMode val="edge"/>
+              <c:yMode val="edge"/>
+              <c:x val="2.1876740216860445E-2"/>
+              <c:y val="0.39214425435655359"/>
+            </c:manualLayout>
+          </c:layout>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1892425040"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr>
+          <a:latin typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+          <a:cs typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+        </a:defRPr>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="1" i="1" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="bg2">
+                    <a:lumMod val="25000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US" b="1" i="1" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="bg2">
+                    <a:lumMod val="25000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+              </a:rPr>
+              <a:t>ES + RLROP</a:t>
+            </a:r>
+            <a:endParaRPr lang="en-US" b="1" i="1" baseline="30000">
+              <a:solidFill>
+                <a:schemeClr val="bg2">
+                  <a:lumMod val="25000"/>
+                </a:schemeClr>
+              </a:solidFill>
+            </a:endParaRPr>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="1" i="1" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="bg2">
+                  <a:lumMod val="25000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout>
+        <c:manualLayout>
+          <c:layoutTarget val="inner"/>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="0.10491983682762546"/>
+          <c:y val="0.12263267998961098"/>
+          <c:w val="0.87299180975871993"/>
+          <c:h val="0.73306160682593824"/>
+        </c:manualLayout>
+      </c:layout>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Comparisons!$E$19</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>F1-Score</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="bg2">
+                <a:lumMod val="25000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="1" i="1" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="bg2">
+                        <a:lumMod val="25000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="en-US"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="outEnd"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:round/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>Comparisons!$D$20:$D$21</c:f>
+              <c:strCache>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>RLROP</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>RLROP + ES</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Comparisons!$E$20:$E$21</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>0.9</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.89</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-4CF3-473E-B221-58B4776AC694}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:dLblPos val="outEnd"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="1"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="219"/>
+        <c:overlap val="-27"/>
+        <c:axId val="1892425040"/>
+        <c:axId val="1892420240"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="1892425040"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1892420240"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="1892420240"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+          <c:max val="1"/>
+          <c:min val="0"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-GB" b="1"/>
+                  <a:t>F1-Score</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:layout>
+            <c:manualLayout>
+              <c:xMode val="edge"/>
+              <c:yMode val="edge"/>
+              <c:x val="2.1876740216860445E-2"/>
+              <c:y val="0.39214425435655359"/>
+            </c:manualLayout>
+          </c:layout>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1892425040"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr>
+          <a:latin typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+          <a:cs typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+        </a:defRPr>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="1" i="1" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:srgbClr val="FF0000"/>
+                </a:solidFill>
+                <a:latin typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US" b="1" i="1">
+                <a:solidFill>
+                  <a:srgbClr val="FF0000"/>
+                </a:solidFill>
+              </a:rPr>
+              <a:t>LR = 1x10</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="en-US" b="1" i="1" baseline="30000">
+                <a:solidFill>
+                  <a:srgbClr val="FF0000"/>
+                </a:solidFill>
+              </a:rPr>
+              <a:t>-4</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="1" i="1" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+              <a:latin typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout>
+        <c:manualLayout>
+          <c:layoutTarget val="inner"/>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="0.10491983682762546"/>
+          <c:y val="0.12263267998961098"/>
+          <c:w val="0.87299180975871993"/>
+          <c:h val="0.73306160682593824"/>
+        </c:manualLayout>
+      </c:layout>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Comparisons!$E$6</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>F1-Score</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="FF0000"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="1" i="1" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:srgbClr val="FF0000"/>
+                    </a:solidFill>
+                    <a:latin typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="en-US"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="outEnd"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:round/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:numRef>
+              <c:f>Comparisons!$D$7:$D$11</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>30</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>45</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>60</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>100</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Comparisons!$E$7:$E$11</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>0.55000000000000004</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.89</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.89</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.88</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.91</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-3CD2-4EE6-9EC4-8EC0E83C2E73}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:dLblPos val="outEnd"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="1"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="219"/>
+        <c:overlap val="-27"/>
+        <c:axId val="1892425040"/>
+        <c:axId val="1892420240"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="1892425040"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-GB" b="1"/>
+                  <a:t>Epoch Size</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1892420240"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="1892420240"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-GB" b="1"/>
+                  <a:t>F1-Score</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:layout>
+            <c:manualLayout>
+              <c:xMode val="edge"/>
+              <c:yMode val="edge"/>
+              <c:x val="2.1876740216860445E-2"/>
+              <c:y val="0.39214425435655359"/>
+            </c:manualLayout>
+          </c:layout>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1892425040"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr>
+          <a:latin typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+          <a:cs typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+        </a:defRPr>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="1" i="1" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:srgbClr val="00B050"/>
+                </a:solidFill>
+                <a:latin typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US" b="1" i="1">
+                <a:solidFill>
+                  <a:srgbClr val="00B050"/>
+                </a:solidFill>
+              </a:rPr>
+              <a:t>LR = 1x10</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="en-US" b="1" i="1" baseline="30000">
+                <a:solidFill>
+                  <a:srgbClr val="00B050"/>
+                </a:solidFill>
+              </a:rPr>
+              <a:t>-5</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="1" i="1" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:srgbClr val="00B050"/>
+              </a:solidFill>
+              <a:latin typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout>
+        <c:manualLayout>
+          <c:layoutTarget val="inner"/>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="0.10491983682762546"/>
+          <c:y val="0.12263267998961098"/>
+          <c:w val="0.87299180975871993"/>
+          <c:h val="0.73306160682593824"/>
+        </c:manualLayout>
+      </c:layout>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Comparisons!$H$6</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>F1-Score</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="00B050"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="1" i="1" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:srgbClr val="00B050"/>
+                    </a:solidFill>
+                    <a:latin typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="en-US"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="outEnd"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:round/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:numRef>
+              <c:f>Comparisons!$G$7:$G$11</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>30</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>45</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>60</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>100</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Comparisons!$H$7:$H$11</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>0.68</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.82</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.82</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.86</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.85</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-73D6-4F84-8A80-9F3C5FC8C0FC}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:dLblPos val="outEnd"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="1"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="219"/>
+        <c:overlap val="-27"/>
+        <c:axId val="1892425040"/>
+        <c:axId val="1892420240"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="1892425040"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-GB" b="1"/>
+                  <a:t>Epoch Size</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1892420240"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="1892420240"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-GB" b="1"/>
+                  <a:t>F1-Score</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:layout>
+            <c:manualLayout>
+              <c:xMode val="edge"/>
+              <c:yMode val="edge"/>
+              <c:x val="2.1876740216860445E-2"/>
+              <c:y val="0.39214425435655359"/>
+            </c:manualLayout>
+          </c:layout>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1892425040"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr>
+          <a:latin typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+          <a:cs typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+        </a:defRPr>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart6.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="1" i="1" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:srgbClr val="0070C0"/>
+                </a:solidFill>
+                <a:latin typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US" b="1" i="1">
+                <a:solidFill>
+                  <a:srgbClr val="0070C0"/>
+                </a:solidFill>
+              </a:rPr>
+              <a:t>LR = 1x10</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="en-US" b="1" i="1" baseline="30000">
+                <a:solidFill>
+                  <a:srgbClr val="0070C0"/>
+                </a:solidFill>
+              </a:rPr>
+              <a:t>-6</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="1" i="1" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:srgbClr val="0070C0"/>
+              </a:solidFill>
+              <a:latin typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout>
+        <c:manualLayout>
+          <c:layoutTarget val="inner"/>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="0.10491983682762546"/>
+          <c:y val="0.12263267998961098"/>
+          <c:w val="0.87299180975871993"/>
+          <c:h val="0.73306160682593824"/>
+        </c:manualLayout>
+      </c:layout>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Comparisons!$K$6</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>F1-Score</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="1" i="1" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:srgbClr val="0070C0"/>
+                    </a:solidFill>
+                    <a:latin typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="en-US"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="outEnd"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:round/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:numRef>
+              <c:f>Comparisons!$J$7:$J$12</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>30</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>45</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>60</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>100</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>200</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Comparisons!$K$7:$K$12</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>0.54</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.69</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.72</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.74</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.76</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.81</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-EAC0-44CB-BB9D-744D09D35262}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:dLblPos val="outEnd"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="1"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="219"/>
+        <c:overlap val="-27"/>
+        <c:axId val="1892425040"/>
+        <c:axId val="1892420240"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="1892425040"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-GB" b="1"/>
+                  <a:t>Epoch Size</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1892420240"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="1892420240"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-GB" b="1"/>
+                  <a:t>F1-Score</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:layout>
+            <c:manualLayout>
+              <c:xMode val="edge"/>
+              <c:yMode val="edge"/>
+              <c:x val="2.1876740216860445E-2"/>
+              <c:y val="0.39214425435655359"/>
+            </c:manualLayout>
+          </c:layout>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1892425040"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr>
+          <a:latin typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+          <a:cs typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+        </a:defRPr>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors3.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors4.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors5.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors6.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="201">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="201">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style3.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="201">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style4.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="201">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style5.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="201">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style6.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="201">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
@@ -186,7 +6408,7 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>7</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
+      <xdr:colOff>273326</xdr:colOff>
       <xdr:row>32</xdr:row>
       <xdr:rowOff>190499</xdr:rowOff>
     </xdr:to>
@@ -203,8 +6425,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="1847850" y="4410074"/>
-          <a:ext cx="2809875" cy="1876425"/>
+          <a:off x="1857789" y="4410074"/>
+          <a:ext cx="3086928" cy="1876425"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -248,6 +6470,81 @@
           </a:r>
         </a:p>
         <a:p>
+          <a:endParaRPr lang="en-GB" sz="1100" u="sng" baseline="0"/>
+        </a:p>
+        <a:p>
+          <a:pPr marL="171450" indent="-171450">
+            <a:buFont typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+            <a:buChar char="•"/>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1100" u="none" baseline="0"/>
+            <a:t>RLROP = 40-50 epochs. Starting LR = 1x10</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1100" u="none" baseline="30000"/>
+            <a:t>-4</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1100" u="none" baseline="0"/>
+            <a:t>  </a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr marL="171450" indent="-171450">
+            <a:buFont typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+            <a:buChar char="•"/>
+          </a:pPr>
+          <a:endParaRPr lang="en-GB" sz="1100" u="none" baseline="0"/>
+        </a:p>
+        <a:p>
+          <a:pPr marL="171450" indent="-171450">
+            <a:buFont typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+            <a:buChar char="•"/>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1100" u="none" baseline="0"/>
+            <a:t>RLROP + ES = ~100 epochs. Starting </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1100" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>LR = 1x10</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1100" baseline="30000">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>-4</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1100" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>  </a:t>
+          </a:r>
+          <a:endParaRPr lang="en-GB" sz="1100" u="none" baseline="0"/>
+        </a:p>
+        <a:p>
           <a:pPr marL="171450" indent="-171450">
             <a:buFont typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
             <a:buChar char="•"/>
@@ -256,6 +6553,230 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>11725</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>63378</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>22</xdr:col>
+      <xdr:colOff>238860</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>182441</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="5" name="Chart 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{56412C39-5B06-E5DA-50A0-8078CEC46B49}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>22</xdr:col>
+      <xdr:colOff>286482</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>62279</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>32</xdr:col>
+      <xdr:colOff>515083</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>181342</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="6" name="Chart 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EC719C15-DE64-4A53-9140-47A128EEB315}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>22</xdr:col>
+      <xdr:colOff>322119</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>20782</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>32</xdr:col>
+      <xdr:colOff>549088</xdr:colOff>
+      <xdr:row>39</xdr:row>
+      <xdr:rowOff>144607</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="8" name="Chart 7">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0C048307-D502-434B-BC73-8FBB337C60C9}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>40300</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>63378</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>22</xdr:col>
+      <xdr:colOff>267435</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>182441</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="9" name="Chart 8">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F25C4407-8EC6-0D25-CD16-FC8DB2E0D170}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId4"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>22</xdr:col>
+      <xdr:colOff>315057</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>62279</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>32</xdr:col>
+      <xdr:colOff>543658</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>181342</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="10" name="Chart 9">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0D5299CD-C3C9-FD02-03C2-0714783187EB}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId5"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>12122</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>36368</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>22</xdr:col>
+      <xdr:colOff>268941</xdr:colOff>
+      <xdr:row>39</xdr:row>
+      <xdr:rowOff>155431</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="11" name="Chart 10">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1B5E2216-1B89-8797-CF0A-A716D89E376E}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId6"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
@@ -576,6 +7097,26 @@
 </a:theme>
 </file>
 
+<file path=xl/webextensions/taskpanes.xml><?xml version="1.0" encoding="utf-8"?>
+<wetp:taskpanes xmlns:wetp="http://schemas.microsoft.com/office/webextensions/taskpanes/2010/11">
+  <wetp:taskpane dockstate="right" visibility="0" width="586" row="1">
+    <wetp:webextensionref xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  </wetp:taskpane>
+</wetp:taskpanes>
+</file>
+
+<file path=xl/webextensions/webextension1.xml><?xml version="1.0" encoding="utf-8"?>
+<we:webextension xmlns:we="http://schemas.microsoft.com/office/webextensions/webextension/2010/11" id="{3DA8F2B4-3506-4DF8-8804-9A3F71989958}">
+  <we:reference id="wa200009404" version="1.0.0.8" store="en-US" storeType="OMEX"/>
+  <we:alternateReferences>
+    <we:reference id="wa200009404" version="1.0.0.8" store="WA200009404" storeType="OMEX"/>
+  </we:alternateReferences>
+  <we:properties/>
+  <we:bindings/>
+  <we:snapshot xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
+</we:webextension>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{157E6442-83B2-458A-A7D7-44481521E105}">
   <dimension ref="D4:K21"/>
@@ -643,7 +7184,9 @@
       <c r="J7" s="2">
         <v>10</v>
       </c>
-      <c r="K7" s="2"/>
+      <c r="K7" s="2">
+        <v>0.54</v>
+      </c>
     </row>
     <row r="8" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D8" s="3">
@@ -661,7 +7204,9 @@
       <c r="J8" s="3">
         <v>30</v>
       </c>
-      <c r="K8" s="3"/>
+      <c r="K8" s="3">
+        <v>0.69</v>
+      </c>
     </row>
     <row r="9" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D9" s="3">
@@ -679,7 +7224,9 @@
       <c r="J9" s="3">
         <v>45</v>
       </c>
-      <c r="K9" s="3"/>
+      <c r="K9" s="3">
+        <v>0.72</v>
+      </c>
     </row>
     <row r="10" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D10" s="3">
@@ -697,7 +7244,9 @@
       <c r="J10" s="3">
         <v>60</v>
       </c>
-      <c r="K10" s="3"/>
+      <c r="K10" s="3">
+        <v>0.74</v>
+      </c>
     </row>
     <row r="11" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D11" s="4">
@@ -715,13 +7264,17 @@
       <c r="J11" s="3">
         <v>100</v>
       </c>
-      <c r="K11" s="3"/>
+      <c r="K11" s="3">
+        <v>0.76</v>
+      </c>
     </row>
     <row r="12" spans="4:11" x14ac:dyDescent="0.25">
       <c r="J12" s="4">
         <v>200</v>
       </c>
-      <c r="K12" s="4"/>
+      <c r="K12" s="4">
+        <v>0.81</v>
+      </c>
     </row>
     <row r="17" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D17" s="1" t="s">
@@ -733,7 +7286,7 @@
     </row>
     <row r="19" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D19" s="1" t="s">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="E19" s="1" t="s">
         <v>1</v>
@@ -743,13 +7296,17 @@
       <c r="D20" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="E20" s="2"/>
+      <c r="E20" s="2">
+        <v>0.9</v>
+      </c>
     </row>
     <row r="21" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D21" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="E21" s="4"/>
+      <c r="E21" s="4">
+        <v>0.89</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
